--- a/vwo.com test case.xlsx
+++ b/vwo.com test case.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C9AE2B2-7F70-4A43-87D7-5E60DBACFFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A5342B-7F2B-4274-80B2-C6D9E0445690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A349E120-5B12-4924-B503-A1BA6F3C61BD}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="282">
   <si>
     <t>test case of vwo.com</t>
   </si>
@@ -451,6 +451,435 @@
   </si>
   <si>
     <t>hide the password when click on passwod visibility icon</t>
+  </si>
+  <si>
+    <t>TC_027</t>
+  </si>
+  <si>
+    <t>TC_028</t>
+  </si>
+  <si>
+    <t>TC_029</t>
+  </si>
+  <si>
+    <t>TC_030</t>
+  </si>
+  <si>
+    <t>TC_031</t>
+  </si>
+  <si>
+    <t>TC_032</t>
+  </si>
+  <si>
+    <t>TC_033</t>
+  </si>
+  <si>
+    <t>TC_034</t>
+  </si>
+  <si>
+    <t>TS_002</t>
+  </si>
+  <si>
+    <t>verify that Email input field is clickable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email field should be cleackable </t>
+  </si>
+  <si>
+    <t>verift that user is enterd email address</t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Forgot password  3. observe Email field  4. click Email field</t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Forgot password  3. click Email field and enter Email address</t>
+  </si>
+  <si>
+    <t>user should be enter Email successfully in Email field</t>
+  </si>
+  <si>
+    <t>verify that placeholder of Email field is display</t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Forgot password  3. observe Email field and check placeholder</t>
+  </si>
+  <si>
+    <t>in Email input field placeholder should be displayed "Enter email ID"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verify that Reset Password button is clickable </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. open vwo.com login page  2. click on Forgot password  3. click Reset Password button </t>
+  </si>
+  <si>
+    <t xml:space="preserve">verify that enter valid Email address user is forgot password successfully </t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Forgot password  3. enter valid credentials  4. click forgot password</t>
+  </si>
+  <si>
+    <t>display one message after clicking on forgot password"If you are registered with us, you will receive a reset email from hello@wingify.com. If you don't see it in your inbox, please check your Spam folder."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verify that after click on Back button user should be redirect on login page </t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Forgot password  3. click Back button</t>
+  </si>
+  <si>
+    <t>user should be redirectes on Login page back</t>
+  </si>
+  <si>
+    <t>TS_003</t>
+  </si>
+  <si>
+    <t>TS_004</t>
+  </si>
+  <si>
+    <t>verify that user is Sign in with valid credentials</t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click Sign in with SSO 3. enter valid Email address</t>
+  </si>
+  <si>
+    <t>TC_035</t>
+  </si>
+  <si>
+    <t>TC_036</t>
+  </si>
+  <si>
+    <t>TC_037</t>
+  </si>
+  <si>
+    <t>TC_038</t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Sign in with SSO  3. click Back button</t>
+  </si>
+  <si>
+    <t>navigation or UI/functional</t>
+  </si>
+  <si>
+    <t>TS_005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verify that business Email field is empty what will the action </t>
+  </si>
+  <si>
+    <t>verify that if enter non business email</t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Free trial 3. observe buttons after emoty field</t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Free trial 3. enter any other Email which is non business Email</t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Free trial 3. enter wrong/invalid Email in Email input field</t>
+  </si>
+  <si>
+    <t>validation/error message should be displayed</t>
+  </si>
+  <si>
+    <t>TC_039</t>
+  </si>
+  <si>
+    <t>TC_040</t>
+  </si>
+  <si>
+    <t>TC_041</t>
+  </si>
+  <si>
+    <t>TC_042</t>
+  </si>
+  <si>
+    <t>TC_043</t>
+  </si>
+  <si>
+    <t>TC_044</t>
+  </si>
+  <si>
+    <t>TC_045</t>
+  </si>
+  <si>
+    <t>TC_046</t>
+  </si>
+  <si>
+    <t>TC_047</t>
+  </si>
+  <si>
+    <t>verify that enter business Email but wrong Email</t>
+  </si>
+  <si>
+    <t>verify that "Create a free trial Account" button remains disabled when check box is unchecked</t>
+  </si>
+  <si>
+    <t>the free trial button should be disable until checkbox is selected</t>
+  </si>
+  <si>
+    <t>functional</t>
+  </si>
+  <si>
+    <t>Verify Free Trial button activation based on second checkbox selection</t>
+  </si>
+  <si>
+    <t>Email field is clickable successfully</t>
+  </si>
+  <si>
+    <t>cuser can write E-mail in email fiels</t>
+  </si>
+  <si>
+    <t>the place holder is displayed "Enter email ID"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reset password button should be clickable </t>
+  </si>
+  <si>
+    <t>Reset Password button is clickable</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> validation message is displayed "If you are registered with us, you will receive a reset email from hello@wingify.com. If you don't see it in your inbox, please check your Spam folder."</t>
+  </si>
+  <si>
+    <t>user is redirected forgot password page to login page</t>
+  </si>
+  <si>
+    <t>verify that after click on Sign in with google google login page should be open</t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Sign in with google button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">user should be redirected on Sign in with google page for choose google account for signin </t>
+  </si>
+  <si>
+    <t xml:space="preserve">user is successfully redirects on Sign in with google page </t>
+  </si>
+  <si>
+    <t>verify that user should be Sign in when choose account</t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Sign in with google button 3. choose an account and Signin with Google Account</t>
+  </si>
+  <si>
+    <t>user should be Sign-in with Google account which is chhosen by user</t>
+  </si>
+  <si>
+    <t>user is redirects on Login page and validation message is display"Your email, password, IP address or location did not match"</t>
+  </si>
+  <si>
+    <t>Check what happens after clicking 'Sign in using SSO'</t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Sign in using SSO button 3. observ the page</t>
+  </si>
+  <si>
+    <t>user should be redirected on SSO login page</t>
+  </si>
+  <si>
+    <t>user is redirect on SSO login page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	The system should display a clear message that SSO is not enabled for the account and instruct the user to sign in using a password.</t>
+  </si>
+  <si>
+    <t>The message “Single Sign-On (SSO) is not enabled for your account. Enter the password to sign in.” is displayed.</t>
+  </si>
+  <si>
+    <t>TC_048</t>
+  </si>
+  <si>
+    <t>TC_049</t>
+  </si>
+  <si>
+    <t>user is back on login page when click on Back button</t>
+  </si>
+  <si>
+    <t>verify that after click on Free trial link user should be redirected on Free trial page for Login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. open vwo.com login page  2. click on Free trial 3. observe the page which is open after click Free trial </t>
+  </si>
+  <si>
+    <t>user should be redirected on Free trial page for login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">user is redirect on Free trial page for login </t>
+  </si>
+  <si>
+    <t>TC_050</t>
+  </si>
+  <si>
+    <t>"Create a Free trial  Account" button is enable so there is no action in empty field</t>
+  </si>
+  <si>
+    <t>the "Create a Free trial  Account" button is disable, can not click without checkbox is check</t>
+  </si>
+  <si>
+    <t>verify that business Email field is empty what will the action when chckbox is check</t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Free trial 3. check the checkboxes and cleck on "Create a Free trial  Account"</t>
+  </si>
+  <si>
+    <t>"A value for this field is required." message is display</t>
+  </si>
+  <si>
+    <t>TC_051</t>
+  </si>
+  <si>
+    <t>"gmail.com doesn't look like a business domain. Please use your business email." message is display</t>
+  </si>
+  <si>
+    <t>"The email address you entered is incorrect." message is display</t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Free trial 3. keep the checkbox  unchecked 4. observe free trial account button</t>
+  </si>
+  <si>
+    <t>Create Free trial Account is disable when check box is unchecked</t>
+  </si>
+  <si>
+    <t>button is become enable when only the second checkbox is selected</t>
+  </si>
+  <si>
+    <t>Button should become enabled when only the second checkbox is selected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Button should remain disabled when only the first checkbox is selected.  </t>
+  </si>
+  <si>
+    <t>Verify Free Trial button activation based on first checkbox selection</t>
+  </si>
+  <si>
+    <t>1. Button is disable when only the first checkbox is selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. open vwo.com login page  2. click on Free trial  3. Select only the first checkbox. 4. Observe the button. </t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Free trial 3.Uncheck the first checkbox and select only the second checkbox. 4. Observe the button again.</t>
+  </si>
+  <si>
+    <t>verify that enter valid Bussiness Email and create Account</t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Free trial 3.enter valid Business Email 4. select checkbox button second checkbox is mendetory 5. click on Create Free trial Account button</t>
+  </si>
+  <si>
+    <t>after click button the detail fields should be display on same page</t>
+  </si>
+  <si>
+    <t>detail input fields are displayed</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verify that all input fields are clickable or not </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. open vwo.com login page  2. click on Free tria 3. check all input fields and observe that fields are clickable or not </t>
+  </si>
+  <si>
+    <t>user can be write details in input fields</t>
+  </si>
+  <si>
+    <t>input fields are clickable and user can write succesfully</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verify that all fields are empty </t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Free tria 3.keep all fields are empty and click on 'Create account'</t>
+  </si>
+  <si>
+    <t>display a validation message for all fields which is required</t>
+  </si>
+  <si>
+    <t>validation message is display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verify that First Name field is empty </t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Free tria 3.keep First Name field is empty</t>
+  </si>
+  <si>
+    <t>validation message should be disply</t>
+  </si>
+  <si>
+    <t>A value for this field is required.' messahe is display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verifty that Last Name field is empty </t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Free tria 3.keep Last Name field is empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verifty that Phone Number field is empty </t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Free tria 3.keep Phone Number field is empty</t>
+  </si>
+  <si>
+    <t>Please enter a valid phone number' message is display</t>
+  </si>
+  <si>
+    <t>verify that enter wrong credentials  in Phone Number field</t>
+  </si>
+  <si>
+    <t>TC_052</t>
+  </si>
+  <si>
+    <t>TC_053</t>
+  </si>
+  <si>
+    <t>TC_054</t>
+  </si>
+  <si>
+    <t>TC_055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. open vwo.com login page  2. click on Free tria 3.enter Wrong Phone Number </t>
+  </si>
+  <si>
+    <t>enter wrong mobile number like "1234567890" validation message should be displayed</t>
+  </si>
+  <si>
+    <t>validation message is not displayed</t>
+  </si>
+  <si>
+    <t>verify that all credential is valid and login</t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Free tria 3.enter valid details in alll fields 4. click on Create account</t>
+  </si>
+  <si>
+    <t>verify that enter more than 10 numbers in Phone Number field</t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Free tria 3.enter more than 10 numbers in Phone Number field</t>
+  </si>
+  <si>
+    <t>display a validation message</t>
+  </si>
+  <si>
+    <t>validation message is display 'Please enter a valid phone number'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verify that in Phone Number field enter cherecters </t>
+  </si>
+  <si>
+    <t>1. open vwo.com login page  2. click on Free tria 3.enter cherecters in Phone Number field like 'hdyrkfshab'</t>
+  </si>
+  <si>
+    <t>conformation message page should be displayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">conformation page is display  </t>
   </si>
 </sst>
 </file>
@@ -572,12 +1001,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -593,13 +1016,19 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -916,7 +1345,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BC1E005-59BB-49DD-9FF8-2F623B05A7A7}">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.88671875" style="1" customWidth="1"/>
@@ -924,7 +1353,7 @@
     <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="30.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="28.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="32.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="33.21875" style="1" customWidth="1"/>
     <col min="7" max="7" width="28.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="11.44140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="13.5546875" style="1" customWidth="1"/>
@@ -933,44 +1362,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-    </row>
-    <row r="3" spans="1:9" s="11" customFormat="1" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+    </row>
+    <row r="3" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="8" t="s">
         <v>7</v>
       </c>
     </row>
@@ -996,10 +1425,10 @@
       <c r="G4" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I4" s="8" t="s">
+      <c r="H4" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1025,10 +1454,10 @@
       <c r="G5" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="5" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1054,10 +1483,10 @@
       <c r="G6" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I6" s="7" t="s">
+      <c r="H6" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1083,10 +1512,10 @@
       <c r="G7" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I7" s="7" t="s">
+      <c r="H7" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1112,14 +1541,14 @@
       <c r="G8" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I8" s="9" t="s">
+      <c r="H8" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -1141,14 +1570,14 @@
       <c r="G9" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I9" s="9" t="s">
+      <c r="H9" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -1170,10 +1599,10 @@
       <c r="G10" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I10" s="9" t="s">
+      <c r="H10" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1199,10 +1628,10 @@
       <c r="G11" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="H11" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I11" s="7" t="s">
+      <c r="H11" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1228,14 +1657,14 @@
       <c r="G12" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I12" s="9" t="s">
+      <c r="H12" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -1257,10 +1686,10 @@
       <c r="G13" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I13" s="7" t="s">
+      <c r="H13" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1286,10 +1715,10 @@
       <c r="G14" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="H14" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I14" s="7" t="s">
+      <c r="H14" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1315,14 +1744,14 @@
       <c r="G15" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="H15" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I15" s="7" t="s">
+      <c r="H15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>41</v>
       </c>
@@ -1344,14 +1773,14 @@
       <c r="G16" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H16" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I16" s="8" t="s">
+      <c r="H16" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>42</v>
       </c>
@@ -1373,10 +1802,10 @@
       <c r="G17" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H17" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I17" s="8" t="s">
+      <c r="H17" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1402,10 +1831,10 @@
       <c r="G18" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="H18" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I18" s="9" t="s">
+      <c r="H18" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I18" s="7" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1431,10 +1860,10 @@
       <c r="G19" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I19" s="9" t="s">
+      <c r="H19" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I19" s="7" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1460,10 +1889,10 @@
       <c r="G20" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H20" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I20" s="8" t="s">
+      <c r="H20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I20" s="6" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1489,10 +1918,10 @@
       <c r="G21" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H21" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I21" s="8" t="s">
+      <c r="H21" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I21" s="6" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1518,10 +1947,10 @@
       <c r="G22" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="H22" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I22" s="9" t="s">
+      <c r="H22" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I22" s="7" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1547,10 +1976,10 @@
       <c r="G23" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="H23" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I23" s="9" t="s">
+      <c r="H23" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I23" s="7" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1576,10 +2005,10 @@
       <c r="G24" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H24" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I24" s="9" t="s">
+      <c r="H24" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I24" s="7" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1605,10 +2034,10 @@
       <c r="G25" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="H25" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I25" s="9" t="s">
+      <c r="H25" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I25" s="7" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1634,10 +2063,10 @@
       <c r="G26" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="H26" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I26" s="9" t="s">
+      <c r="H26" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I26" s="7" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1663,10 +2092,10 @@
       <c r="G27" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="H27" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I27" s="9" t="s">
+      <c r="H27" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I27" s="7" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1692,10 +2121,10 @@
       <c r="G28" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I28" s="7" t="s">
+      <c r="H28" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I28" s="5" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1721,23 +2150,919 @@
       <c r="G29" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="H29" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I29" s="9" t="s">
+      <c r="H29" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I29" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
+    <row r="30" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="G58" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" s="12"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+      <c r="I59" s="12"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" s="12"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
+      <c r="I60" s="12"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" s="12"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+      <c r="I61" s="12"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" s="12"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" s="12"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="12"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" s="12"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
+      <c r="I64" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
